--- a/SubRES_TMPL/SubRES_PWR_ElectricityStorage.xlsx
+++ b/SubRES_TMPL/SubRES_PWR_ElectricityStorage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\SELFS_CRPEMIS_FIX2609\SELFS_CRPEMIS_FIX2609\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AA10AF-B649-4147-84CA-E7DBF191C680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D3F6B1-A706-4DBF-AC7C-01256C8CD993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -4108,6 +4108,8 @@
     <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" customWidth="1"/>
     <col min="10" max="10" width="20.453125" customWidth="1"/>
     <col min="11" max="11" width="43.7265625" customWidth="1"/>
     <col min="12" max="13" width="11.26953125" bestFit="1" customWidth="1"/>
